--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -899,7 +899,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>4.14pm</t>
+          <t>4.44pm</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>7.50pm · Dinner near Indian Music Experience Museum</t>
+          <t>7.40pm · Dinner near Indian Music Experience Museum</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.55am</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1259,10 +1259,14 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>10.20pm · Dinner near Sabha Bengaluru (late return)</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr"/>
+          <t>10.10pm · Dinner near Sabha Bengaluru (late return)</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>2 of 25 artists travel today; 23 stay at the stay.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1301,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1363,12 +1367,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>4.14pm</t>
+          <t>4.44pm</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1385,132 +1389,78 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>6.00pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>5.40pm</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>6.00pm</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>7.30pm</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>LECTURE DEMONSTRATION</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Talk · Indian Music Experience Museum, JP Nagar 7th Phase · 2 artists</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>7.40pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>LECTURE DEMONSTRATION</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Talk · Indian Music Experience Museum, JP Nagar 7th Phase · 25 artists</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>7.35pm</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>7.35pm</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>7.50pm</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>7.50pm</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>8.50pm</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>7.40pm</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>8.40pm</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Dinner near Indian Music Experience Museum</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>
@@ -4830,7 +4780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4885,12 +4835,12 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.55am</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>10.20am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -4900,24 +4850,24 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>14 min · 5 km · typical traffic for the day · 10 min loading first</t>
+          <t>15 min · 5 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>10.20am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.59am</t>
+          <t>10.30am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
@@ -4925,154 +4875,100 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.59am</t>
+          <t>10.30am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>10.09am</t>
+          <t>11.00am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Spare time at the venue</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>10.09am</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>10.29am</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>11.00am</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>10.00pm</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>CLOSING DAY</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Talk · Sabha Bengaluru, Shivajinagar · 2 artists</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>10.29am</t>
+          <t>12.00pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>11.00am</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>11.00am</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>During “Closing Day” — arrange packed lunch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>10.00pm</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>CLOSING DAY</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Talk · Sabha Bengaluru, Shivajinagar · 25 artists</t>
-        </is>
-      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>10.10pm</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>10.10pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>1.00pm</t>
+          <t>11.10pm</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>During “Closing Day” — arrange packed lunch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>10.05pm</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>10.05pm</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>10.20pm</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>10.20pm</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>11.20pm</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
           <t>Dinner near Sabha Bengaluru (late return)</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr"/>
+      <c r="D12" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -839,10 +839,14 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>10.20pm · Dinner near PCPA (Prestige Centre for Performing Arts) (late return)</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr"/>
+          <t>9.20pm · Dinner near PCPA (Prestige Centre for Performing Arts)</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -872,12 +876,12 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>10.20pm · Dinner near PCPA (Prestige Centre for Performing Arts) (late return)</t>
+          <t>9.20pm · Dinner near PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Short night: 6 h 03 between lights out (12.57am (+1)) and wake-up.</t>
+          <t>Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6252,82 +6256,71 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>• Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Where / detail</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>4.17pm</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>5.24pm</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>→ Leave the stay for PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>57 min · 13 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>5.24pm</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>5.34pm</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
+          <t>5.24pm</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
           <t>5.34pm</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>5.44pm</t>
-        </is>
-      </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
@@ -6335,75 +6328,75 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
+          <t>5.34pm</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
           <t>5.44pm</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>5.44pm</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>5.59pm</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>KECAK WORKSHOP</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Workshop · PCPA (Prestige Centre for Performing Arts), Konanakunte, Kanakapura Road · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>10.05pm</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>10.05pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>9.05pm</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr"/>
@@ -6411,22 +6404,47 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>9.05pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
           <t>10.20pm</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>11.20pm</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near PCPA (Prestige Centre for Performing Arts) (late return)</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near PCPA (Prestige Centre for Performing Arts)</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>added: the plan has dinner back at the stay</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6438,7 +6456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6468,82 +6486,71 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>• Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Where / detail</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>4.18pm</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>5.25pm</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>→ Leave the stay for PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>57 min · 13 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>5.25pm</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>5.35pm</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
+          <t>5.25pm</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
           <t>5.35pm</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>5.45pm</t>
-        </is>
-      </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
@@ -6551,75 +6558,75 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
+          <t>5.35pm</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
           <t>5.45pm</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>5.45pm</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>KECAK WORKSHOP</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Workshop · PCPA (Prestige Centre for Performing Arts), Konanakunte, Kanakapura Road · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>10.05pm</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>10.05pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>9.05pm</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr"/>
@@ -6627,22 +6634,47 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>9.05pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
           <t>10.20pm</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>11.20pm</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near PCPA (Prestige Centre for Performing Arts) (late return)</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near PCPA (Prestige Centre for Performing Arts)</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>added: the plan has dinner back at the stay</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -935,7 +935,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Workshop for Students 10.00am; Traditional Balinese Dance 7.00pm</t>
+          <t>Workshop for Students 10.00am; Traditional Balinese Dance 5.00pm</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>9.20pm · Dinner near Meenakshi Rangamancha</t>
+          <t>7.20pm · Dinner near Meenakshi Rangamancha</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Workshop for Students 10.00am · Traditional Balinese Dance 7.00pm</t>
+          <t>Workshop for Students 10.00am · Traditional Balinese Dance 5.00pm</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>2.46pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1735,12 +1735,12 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>2.46pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>3.00pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -1750,19 +1750,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>15 min · 5 km · typical traffic for the day</t>
+          <t>14 min · 5 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>3.00pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1775,12 +1775,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1793,12 +1793,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1811,12 +1811,12 @@
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -1833,12 +1833,12 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>6.50pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1851,12 +1851,12 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>6.50pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1869,12 +1869,12 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -729,12 +729,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>An Evening of Kecak - Inaugural Public Performance 6.00pm</t>
+          <t>An Evening of Kecak - Inaugural Public Performance 5.30pm</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>3.05pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>8.20pm · Dinner near Orion Mall</t>
+          <t>7.50pm · Dinner near Orion Mall</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Dance Movement Workshop 9.00am; Indonesian Shadow Puppetry Performance 3.30pm</t>
+          <t>Dance Movement Workshop 9.00am; Shadow Puppetry Performance 3.30pm</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>“Indonesian Shadow Puppetry Performance”: arrives 1.51pm, 21 min late for the 120 min preparation.</t>
+          <t>“Shadow Puppetry Performance”: arrives 1.51pm, 21 min late for the 120 min preparation.</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Balinese Shadow Puppetry Workshop 10.00am; Kecak Performance 7.00pm</t>
+          <t>Shadow Puppetry Workshop 10.00am; Kecak Performance 5.30pm</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>9.20pm · Dinner near PCPA (Prestige Centre for Performing Arts)</t>
+          <t>7.50pm · Dinner near PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Balinese Shadow Puppetry Workshop 10.00am; Indonesian × Indian Shadow Puppetry Performance 7.30pm</t>
+          <t>Shadow Puppetry Workshop 10.00am; Indonesian × Indian Puppetry Act 6.30pm</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1045,10 +1045,14 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>9.50pm · Dinner near Mandala Cultural Centre (late return)</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr"/>
+          <t>8.50pm · Dinner near Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1063,12 +1067,12 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Traditional Balinese Dance × Yakshagana Performance 7.00pm</t>
+          <t>Traditional Balinese Dance × Yakshagana Performance 6.00pm</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>4.05pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1078,7 +1082,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>9.50pm · Dinner near Chowdiah Memorial Hall</t>
+          <t>8.20pm · Dinner near Chowdiah Memorial Hall</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -1100,7 +1104,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Mask Making Workshop 10.00am; Gamelan workshop 6.00pm</t>
+          <t>Mask Making Workshop 10.00am; Gamelan workshop 5.00pm</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -2010,7 +2014,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Balinese Shadow Puppetry Workshop 10.00am · Kecak Performance 7.00pm</t>
+          <t>Shadow Puppetry Workshop 10.00am · Kecak Performance 5.30pm</t>
         </is>
       </c>
     </row>
@@ -2150,12 +2154,12 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>BALINESE SHADOW PUPPETRY WORKSHOP</t>
+          <t>SHADOW PUPPETRY WORKSHOP</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road · 25 artists</t>
+          <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2207,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>4.28pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -2234,12 +2238,12 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>4.28pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>4.46pm</t>
+          <t>3.14pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -2249,19 +2253,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>18 min · 5 km · typical traffic for the day</t>
+          <t>17 min · 5 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>4.46pm</t>
+          <t>3.14pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>3.59pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -2274,12 +2278,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>3.59pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.01pm</t>
+          <t>4.29pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2292,12 +2296,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.01pm</t>
+          <t>4.29pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2310,12 +2314,12 @@
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
           <t>7.00pm</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>8.30pm</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -2332,12 +2336,12 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -2350,12 +2354,12 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -2368,12 +2372,12 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>8.50pm</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -2428,86 +2432,75 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Balinese Shadow Puppetry Workshop 10.00am · Indonesian × Indian Shadow Puppetry Performance 7.30pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+          <t>Shadow Puppetry Workshop 10.00am · Indonesian × Indian Puppetry Act 6.30pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>• Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Where / detail</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>8.30am</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>9.21am</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>→ Leave the stay for Mandala Cultural Centre</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>41 min · 25 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>9.21am</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>9.31am</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
+          <t>9.21am</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
           <t>9.31am</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>9.41am</t>
-        </is>
-      </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
@@ -2515,17 +2508,17 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
+          <t>9.31am</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
           <t>9.41am</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>9.56am</t>
-        </is>
-      </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
@@ -2533,115 +2526,111 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
+          <t>9.41am</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
           <t>9.56am</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>9.56am</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Spare time at the venue</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>1.00pm</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>BALINESE SHADOW PUPPETRY WORKSHOP</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road · 25 artists</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>1.05pm</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY WORKSHOP</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
           <t>1.05pm</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>1.05pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>1.20pm</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>2.05pm</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>→ Back to the stay</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>45 min · 23 km · typical traffic for the day</t>
-        </is>
-      </c>
+      <c r="D14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>2.05pm</t>
+          <t>1.20pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>4.29pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>At the stay — rest</t>
+          <t>Hold at Mandala Cultural Centre</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
@@ -2649,17 +2638,17 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>2.05pm</t>
+          <t>1.20pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>3.05pm</t>
+          <t>2.20pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Lunch at the stay</t>
+          <t>Lunch near Mandala Cultural Centre</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr"/>
@@ -2667,34 +2656,34 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>4.29pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>→ Leave the stay for Mandala Cultural Centre</t>
+          <t>→ Leave Mandala Cultural Centre for Mandala Cultural Centre</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>51 min · 25 km · typical traffic for the day · 10 min loading first</t>
+          <t>0 min · 0 km</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -2707,12 +2696,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.30pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2725,12 +2714,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
           <t>6.30pm</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2743,34 +2732,34 @@
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>INDONESIAN × INDIAN SHADOW PUPPETRY PERFORMANCE</t>
+          <t>INDONESIAN × INDIAN PUPPETRY ACT</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Performance · Mandala Cultural Centre, Talaghattapura, Kanakapura Road · 25 artists</t>
+          <t>Performance · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -2783,12 +2772,12 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>8.50pm</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -2801,22 +2790,29 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Dinner near Mandala Cultural Centre (late return)</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr"/>
+          <t>Dinner near Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>added: the plan has dinner back at the stay</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2854,7 +2850,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Traditional Balinese Dance × Yakshagana Performance 7.00pm</t>
+          <t>Traditional Balinese Dance × Yakshagana Performance 6.00pm</t>
         </is>
       </c>
     </row>
@@ -2897,12 +2893,12 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>4.05pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>3.33pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -2912,19 +2908,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>17 min · 4 km · typical traffic for the day · 10 min loading first</t>
+          <t>18 min · 4 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>3.33pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>4.03pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2937,12 +2933,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>4.03pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>4.33pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2955,12 +2951,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>4.33pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>6.32pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -2973,12 +2969,12 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>6.32pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>6.00pm</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -2991,12 +2987,12 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>6.00pm</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -3013,12 +3009,12 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -3031,12 +3027,12 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -3049,12 +3045,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>10.50pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -3084,7 +3080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3110,7 +3106,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Mask Making Workshop 10.00am · Gamelan workshop 6.00pm</t>
+          <t>Mask Making Workshop 10.00am · Gamelan workshop 5.00pm</t>
         </is>
       </c>
     </row>
@@ -3296,99 +3292,95 @@
       <c r="D14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>1.49pm</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>→ Back to the stay</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>29 min · 8 km · typical traffic for the day</t>
-        </is>
-      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>4.16pm</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Hold in town near PARSEC, Jayanagar (Maker's Adda)</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.49pm</t>
+          <t>1.20pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>4.53pm</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>At the stay — rest</t>
+          <t>2.20pm</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Lunch near PARSEC, Jayanagar (Maker's Adda)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>1.49pm</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>2.49pm</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Lunch at the stay</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr"/>
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>4.16pm</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>4.25pm</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>→ Leave PARSEC, Jayanagar (Maker's Adda) for Jama The Studio</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>9 min · 2 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>4.30pm</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>5.09pm</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Jama The Studio</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>29 min · 7 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>4.25pm</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>4.35pm</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>4.35pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr"/>
@@ -3396,132 +3388,96 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>5.29pm</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>5.44pm</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>GAMELAN WORKSHOP</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Workshop · Jama The Studio, Jayanagar 2nd Block · 25 artists</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>8.05pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Spare time at the venue</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>8.00pm</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>GAMELAN WORKSHOP</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Workshop · Jama The Studio, Jayanagar 2nd Block · 25 artists</t>
-        </is>
-      </c>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>8.05pm</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>8.05pm</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>8.05pm</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>8.20pm</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>8.20pm</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Dinner near Jama The Studio</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D24" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>
@@ -5511,7 +5467,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>An Evening of Kecak - Inaugural Public Performance 6.00pm</t>
+          <t>An Evening of Kecak - Inaugural Public Performance 5.30pm</t>
         </is>
       </c>
     </row>
@@ -5547,12 +5503,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>3.05pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.40pm</t>
+          <t>3.10pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5569,12 +5525,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
+          <t>3.10pm</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
           <t>3.40pm</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>4.10pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5587,12 +5543,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
+          <t>3.40pm</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
           <t>4.10pm</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>4.40pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5605,12 +5561,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.10pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.10pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5623,12 +5579,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.10pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -5641,12 +5597,12 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -5663,12 +5619,12 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>7.50pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -5681,12 +5637,12 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
+          <t>7.20pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
           <t>7.50pm</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>8.20pm</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -5699,12 +5655,12 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>8.50pm</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
@@ -5759,7 +5715,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dance Movement Workshop 9.00am · Indonesian Shadow Puppetry Performance 3.30pm</t>
+          <t>Dance Movement Workshop 9.00am · Shadow Puppetry Performance 3.30pm</t>
         </is>
       </c>
     </row>
@@ -6048,12 +6004,12 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>INDONESIAN SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Performance · Jagriti Theatre, Whitefield · 25 artists</t>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
     </row>
@@ -6070,12 +6026,12 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>INDONESIAN SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Performance · Jagriti Theatre, Whitefield · 25 artists</t>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -829,7 +829,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>8.20pm · Dinner near Jama The Studio</t>
+          <t>7.50pm · Dinner near Jama The Studio</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -3428,12 +3428,12 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>8.05pm</t>
+          <t>7.35pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -3446,12 +3446,12 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>8.05pm</t>
+          <t>7.35pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -3464,12 +3464,12 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>8.50pm</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h · 33 km · typical traffic for the day · 10 min loading first</t>
+          <t>1 h · 33 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.10pm</t>
+          <t>3.09pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5518,19 +5518,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>25 min · 6 km · typical traffic for the day · 10 min loading first</t>
+          <t>24 min · 6 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.10pm</t>
+          <t>3.09pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.40pm</t>
+          <t>3.39pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5543,12 +5543,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.40pm</t>
+          <t>3.39pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.10pm</t>
+          <t>4.09pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5561,12 +5561,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.10pm</t>
+          <t>4.09pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.10pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5579,7 +5579,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.10pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6244,12 +6244,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.24pm</t>
+          <t>5.25pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6266,12 +6266,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.24pm</t>
+          <t>5.25pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.34pm</t>
+          <t>5.35pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6284,12 +6284,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.34pm</t>
+          <t>5.35pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.45pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6302,12 +6302,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.45pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.59pm</t>
+          <t>6.00pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6474,7 +6474,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>57 min · 13 km · typical traffic for the day · 10 min loading first</t>
+          <t>58 min · 13 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -4674,7 +4674,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4684,19 +4684,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h · 33 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>40 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.55pm</t>
+          <t>6.35pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>10.20am</t>
+          <t>10.21am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -4810,19 +4810,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>15 min · 5 km · typical traffic for the day · 10 min loading first</t>
+          <t>16 min · 5 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>10.20am</t>
+          <t>10.21am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>10.30am</t>
+          <t>10.31am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -4835,7 +4835,7 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>10.30am</t>
+          <t>10.31am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>39 min · 25 km · typical traffic for the day · 10 min loading first</t>
+          <t>39 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.27am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,19 +5265,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>39 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>37 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.27am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.39am</t>
+          <t>6.37am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5290,12 +5290,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.39am</t>
+          <t>6.37am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.54am</t>
+          <t>6.52am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.54am</t>
+          <t>6.52am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>24 min · 6 km · typical traffic for the day · 10 min loading first</t>
+          <t>24 min · 6 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -4674,7 +4674,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.05pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4684,19 +4684,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>40 min · 34 km · live traffic · 10 min loading first</t>
+          <t>39 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.05pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.35pm</t>
+          <t>6.34pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.27am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,19 +5265,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>37 min · 25 km · live traffic · 10 min loading first</t>
+          <t>33 min · 19 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.27am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.37am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5290,12 +5290,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.37am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.52am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.52am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>21 min · 11 km · typical traffic for the day · 10 min loading first</t>
+          <t>21 min · 11 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>1 h 01 · 26 km · typical traffic for the day</t>
+          <t>1 h 01 · 26 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -4674,7 +4674,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4684,19 +4684,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>39 min · 34 km · live traffic · 10 min loading first</t>
+          <t>40 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.34pm</t>
+          <t>6.35pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,19 +5265,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>33 min · 19 km · live traffic · 10 min loading first</t>
+          <t>32 min · 19 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5290,12 +5290,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.09pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5518,19 +5518,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>24 min · 6 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>12 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.09pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.39pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5543,12 +5543,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.39pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.09pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5561,12 +5561,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.09pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5579,7 +5579,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -784,11 +784,7 @@
           <t>9.50pm · Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>“Shadow Puppetry Performance”: arrives 1.51pm, 21 min late for the 120 min preparation.</t>
-        </is>
-      </c>
+      <c r="G10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -898,12 +894,12 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Lecture Demonstration 6.00pm</t>
+          <t>Lecture Demonstration 5.00pm</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>4.44pm</t>
+          <t>3.46pm</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -913,7 +909,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>7.40pm · Dinner near Indian Music Experience Museum</t>
+          <t>6.40pm · Dinner near Indian Music Experience Museum</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -960,23 +956,35 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Sat, 10 Oct</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Rest day</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr"/>
-      <c r="D16" s="7" t="inlineStr"/>
-      <c r="E16" s="7" t="inlineStr"/>
-      <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Rest day at the stay · no travel</t>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Show day</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Dance Movement Workshop - 2 4.00pm</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>2.30pm</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>7.20pm · Dinner before leaving</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1347,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Lecture Demonstration 6.00pm</t>
+          <t>Lecture Demonstration 5.00pm</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1383,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>4.44pm</t>
+          <t>3.46pm</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>4.50pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1390,19 +1398,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>56 min · 13 km · typical traffic for the day · 10 min loading first</t>
+          <t>54 min · 13 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>4.50pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1415,12 +1423,12 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -1437,12 +1445,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>7.40pm</t>
+          <t>6.40pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1455,12 +1463,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
+          <t>6.40pm</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
           <t>7.40pm</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>8.40pm</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
@@ -1907,7 +1915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1933,14 +1941,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Rest day at the stay</t>
+          <t>Dance Movement Workshop - 2 4.00pm</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>• Rest day at the stay · no travel</t>
+          <t>• Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
         </is>
       </c>
     </row>
@@ -1967,9 +1975,158 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Rest day at the stay · no travel</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>2.30pm</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>3.25pm</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>→ Leave the stay for MLA College, Malleswaram</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>travel time unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>3.25pm</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>3.35pm</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>3.35pm</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>3.45pm</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>3.45pm</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>7.00pm</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>DANCE MOVEMENT WORKSHOP - 2</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>7.00pm</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>7.05pm</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>7.05pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>7.20pm</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>7.20pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Dinner before leaving</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>added: the plan has dinner back at the stay</t>
         </is>
       </c>
     </row>
@@ -4674,7 +4831,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.05pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4684,19 +4841,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>40 min · 34 km · live traffic · 10 min loading first</t>
+          <t>38 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.05pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.35pm</t>
+          <t>6.33pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5255,7 +5412,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,19 +5422,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>32 min · 19 km · live traffic · 10 min loading first</t>
+          <t>33 min · 19 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5290,12 +5447,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5308,7 +5465,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5689,7 +5846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5749,7 +5906,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.01am</t>
+          <t>7.56am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5759,19 +5916,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>21 min · 11 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>16 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.01am</t>
+          <t>7.56am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.11am</t>
+          <t>8.06am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5784,12 +5941,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.11am</t>
+          <t>8.06am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.21am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5802,12 +5959,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.21am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5820,7 +5977,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -5923,7 +6080,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.51pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -5933,19 +6090,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>1 h 01 · 26 km · traffic, refreshed hourly</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.51pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.21pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -5958,12 +6115,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.21pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -5976,97 +6133,97 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6074,20 +6231,38 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6259,7 +6434,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>57 min · 13 km · typical traffic for the day · 10 min loading first</t>
+          <t>57 min · 13 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -784,7 +784,11 @@
           <t>9.50pm · Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>“Shadow Puppetry Performance”: arrives 1.40pm, 10 min late for the 120 min preparation.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -4831,7 +4835,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.06pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4841,19 +4845,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>38 min · 34 km · live traffic · 10 min loading first</t>
+          <t>41 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.06pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.33pm</t>
+          <t>6.36pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5412,7 +5416,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.27am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5422,19 +5426,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>33 min · 19 km · live traffic · 10 min loading first</t>
+          <t>37 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.27am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.37am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5447,12 +5451,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.37am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.52am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5465,7 +5469,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.52am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5665,7 +5669,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.59pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5675,19 +5679,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>12 min · 7 km · live traffic · 10 min loading first</t>
+          <t>14 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.59pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.29pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5700,12 +5704,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.29pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.59pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5718,12 +5722,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.59pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.59pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5736,7 +5740,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.59pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5846,7 +5850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5906,7 +5910,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>7.56am</t>
+          <t>7.58am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5916,19 +5920,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>16 min · 11 km · live traffic · 10 min loading first</t>
+          <t>18 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>7.56am</t>
+          <t>7.58am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.06am</t>
+          <t>8.08am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5941,12 +5945,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.06am</t>
+          <t>8.08am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5959,12 +5963,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5977,7 +5981,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6080,7 +6084,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>1.40pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6090,19 +6094,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>50 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>1.40pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.10pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6115,12 +6119,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.10pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.40pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6133,12 +6137,12 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.40pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -6148,38 +6152,42 @@
       </c>
       <c r="D18" s="7" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>3.28pm</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr"/>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -6188,42 +6196,38 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6231,38 +6235,20 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6664,7 +6650,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>58 min · 13 km · typical traffic for the day · 10 min loading first</t>
+          <t>58 min · 13 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -784,11 +784,7 @@
           <t>9.50pm · Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>“Shadow Puppetry Performance”: arrives 1.40pm, 10 min late for the 120 min preparation.</t>
-        </is>
-      </c>
+      <c r="G10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -829,7 +825,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1402,7 +1398,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>54 min · 13 km · typical traffic for the day · 10 min loading first</t>
+          <t>54 min · 13 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4835,7 +4831,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.06pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4845,19 +4841,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>41 min · 34 km · live traffic · 10 min loading first</t>
+          <t>39 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.06pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.36pm</t>
+          <t>6.34pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5416,7 +5412,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.27am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5426,19 +5422,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>37 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 19 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.27am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.37am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5451,12 +5447,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.37am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.52am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5469,7 +5465,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.52am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5669,7 +5665,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>2.59pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5679,19 +5675,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>14 min · 7 km · live traffic · 10 min loading first</t>
+          <t>13 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2.59pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.29pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5704,12 +5700,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.29pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3.59pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5722,12 +5718,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>3.59pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.59pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5740,7 +5736,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.59pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5910,7 +5906,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>7.58am</t>
+          <t>7.57am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5920,19 +5916,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>18 min · 11 km · live traffic · 10 min loading first</t>
+          <t>17 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>7.58am</t>
+          <t>7.57am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.08am</t>
+          <t>8.07am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5945,12 +5941,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.08am</t>
+          <t>8.07am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5963,12 +5959,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.33am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5981,7 +5977,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.33am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6084,7 +6080,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.40pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6094,19 +6090,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>50 min · 29 km · live traffic</t>
+          <t>43 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.40pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.10pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6119,12 +6115,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.10pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.40pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6137,7 +6133,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.40pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -6343,7 +6339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6405,12 +6401,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6420,19 +6416,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>57 min · 13 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>28 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6445,12 +6441,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6463,75 +6459,75 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
+          <t>5.43pm</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>5.43pm</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>KECAK WORKSHOP</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Workshop · PCPA (Prestige Centre for Performing Arts), Konanakunte, Kanakapura Road · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>9.05pm</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
           <t>9.05pm</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
@@ -6539,20 +6535,38 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
+          <t>9.05pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>10.20pm</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Dinner near PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -862,7 +862,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.50pm</t>
+          <t>4.49pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1398,19 +1398,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>54 min · 13 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>53 min · 13 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.50pm</t>
+          <t>4.49pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>4.59pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>42 min · 16 km · typical traffic for the day · 10 min loading first</t>
+          <t>42 min · 16 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>14 min · 5 km · typical traffic for the day</t>
+          <t>14 min · 5 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4841,19 +4841,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>39 min · 34 km · live traffic · 10 min loading first</t>
+          <t>40 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.34pm</t>
+          <t>6.35pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>10.21am</t>
+          <t>10.20am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -4967,19 +4967,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>16 min · 5 km · typical traffic for the day · 10 min loading first</t>
+          <t>15 min · 5 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>10.21am</t>
+          <t>10.20am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>10.31am</t>
+          <t>10.30am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -4992,7 +4992,7 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>10.31am</t>
+          <t>10.30am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.34pm</t>
+          <t>9.35pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5205,14 +5205,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>54 min · 33 km · typical traffic for the day</t>
+          <t>55 min · 33 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.34pm</t>
+          <t>9.35pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.26am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5422,19 +5422,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>35 min · 19 km · live traffic · 10 min loading first</t>
+          <t>36 min · 19 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.26am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.36am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5447,12 +5447,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.36am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.51am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5465,7 +5465,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.51am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>7.57am</t>
+          <t>7.58am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5916,19 +5916,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>17 min · 11 km · live traffic · 10 min loading first</t>
+          <t>18 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>7.57am</t>
+          <t>7.58am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.07am</t>
+          <t>8.08am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5941,12 +5941,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.07am</t>
+          <t>8.08am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5959,12 +5959,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.32am</t>
+          <t>8.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5977,7 +5977,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.32am</t>
+          <t>8.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6090,19 +6090,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>43 min · 29 km · live traffic</t>
+          <t>44 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>2.04pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6115,12 +6115,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>2.04pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6133,7 +6133,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6416,19 +6416,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 14 km · live traffic · 10 min loading first</t>
+          <t>29 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6441,12 +6441,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6459,12 +6459,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6477,7 +6477,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6587,7 +6587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6649,12 +6649,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6664,19 +6664,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>58 min · 13 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>29 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6689,12 +6689,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6707,75 +6707,75 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
+          <t>5.44pm</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>5.44pm</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>KECAK WORKSHOP</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Workshop · PCPA (Prestige Centre for Performing Arts), Konanakunte, Kanakapura Road · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>9.05pm</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
           <t>9.05pm</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
@@ -6783,20 +6783,38 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
+          <t>9.05pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>10.20pm</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Dinner near PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -784,7 +784,11 @@
           <t>9.50pm · Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>“Shadow Puppetry Performance”: arrives 1.36pm, 6 min late for the 120 min preparation.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -899,7 +903,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>3.46pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1321,7 +1325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1383,12 +1387,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>3.46pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.49pm</t>
+          <t>4.32pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1398,19 +1402,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>53 min · 13 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>27 min · 13 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.49pm</t>
+          <t>4.32pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.59pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1420,63 +1424,81 @@
       </c>
       <c r="D8" s="7" t="inlineStr"/>
     </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>4.42pm</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>LECTURE DEMONSTRATION</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Talk · Indian Music Experience Museum, JP Nagar 7th Phase · 2 artists</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>6.30pm</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>6.40pm</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
           <t>6.40pm</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>6.40pm</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>7.40pm</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>Dinner near Indian Music Experience Museum</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>
@@ -5422,7 +5444,7 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>36 min · 19 km · live traffic · 10 min loading first</t>
+          <t>36 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5928,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>7.58am</t>
+          <t>7.57am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5916,19 +5938,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>18 min · 11 km · live traffic · 10 min loading first</t>
+          <t>17 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>7.58am</t>
+          <t>7.57am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.08am</t>
+          <t>8.07am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5941,12 +5963,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.08am</t>
+          <t>8.07am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5959,12 +5981,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.33am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5977,7 +5999,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.33am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6080,7 +6102,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.36pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6090,19 +6112,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>44 min · 26 km · live traffic</t>
+          <t>46 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.36pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.04pm</t>
+          <t>2.06pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6115,12 +6137,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.04pm</t>
+          <t>2.06pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.36pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6133,7 +6155,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.36pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -6406,7 +6428,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6416,19 +6438,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>29 min · 14 km · live traffic · 10 min loading first</t>
+          <t>31 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6441,12 +6463,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6459,12 +6481,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.46pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6477,7 +6499,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.46pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6654,7 +6676,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6664,19 +6686,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>29 min · 14 km · live traffic · 10 min loading first</t>
+          <t>31 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6689,12 +6711,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6707,12 +6729,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.46pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6725,7 +6747,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.46pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -784,11 +784,7 @@
           <t>9.50pm · Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>“Shadow Puppetry Performance”: arrives 1.36pm, 6 min late for the 120 min preparation.</t>
-        </is>
-      </c>
+      <c r="G10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1392,7 +1388,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1402,19 +1398,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 13 km · live traffic · 10 min loading first</t>
+          <t>26 min · 13 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1427,7 +1423,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -1586,7 +1582,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1596,19 +1592,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>42 min · 16 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>28 min · 12 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1621,12 +1617,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1639,12 +1635,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.57am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1657,7 +1653,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.57am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -1738,7 +1734,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.46pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1769,7 +1765,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.46pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1784,7 +1780,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>14 min · 5 km · traffic, refreshed hourly</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2240,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>40 min · 25 km · typical traffic for the day · 10 min loading first</t>
+          <t>40 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2428,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>17 min · 5 km · typical traffic for the day</t>
+          <t>17 min · 5 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5430,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.26am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5444,19 +5440,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>36 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 19 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.26am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.36am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5469,12 +5465,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.36am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.51am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5487,7 +5483,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.51am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5687,7 +5683,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5697,19 +5693,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>13 min · 7 km · live traffic · 10 min loading first</t>
+          <t>12 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5722,12 +5718,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5740,12 +5736,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5758,7 +5754,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6102,7 +6098,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.36pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6112,19 +6108,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>46 min · 26 km · live traffic</t>
+          <t>44 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.36pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.06pm</t>
+          <t>2.04pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6137,12 +6133,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.06pm</t>
+          <t>2.04pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.36pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6155,7 +6151,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.36pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -6428,7 +6424,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6438,19 +6434,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>31 min · 14 km · live traffic · 10 min loading first</t>
+          <t>28 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6463,12 +6459,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6481,12 +6477,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.46pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6499,7 +6495,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.46pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6676,7 +6672,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6686,19 +6682,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>31 min · 14 km · live traffic · 10 min loading first</t>
+          <t>28 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6711,12 +6707,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6729,12 +6725,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.46pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6747,7 +6743,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.46pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1398,19 +1398,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>26 min · 13 km · live traffic · 10 min loading first</t>
+          <t>25 min · 13 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1423,7 +1423,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1592,19 +1592,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 12 km · live traffic · 10 min loading first</t>
+          <t>26 min · 12 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1617,12 +1617,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2658,19 +2658,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>41 min · 25 km · typical traffic for the day · 10 min loading first</t>
+          <t>42 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2683,12 +2683,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2701,12 +2701,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.56am</t>
+          <t>9.57am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2719,7 +2719,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.56am</t>
+          <t>9.57am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.05pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4859,19 +4859,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>40 min · 34 km · live traffic · 10 min loading first</t>
+          <t>39 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.05pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.35pm</t>
+          <t>6.34pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5440,19 +5440,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>35 min · 19 km · live traffic · 10 min loading first</t>
+          <t>33 min · 19 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5465,12 +5465,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5483,7 +5483,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5693,19 +5693,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>12 min · 7 km · live traffic · 10 min loading first</t>
+          <t>13 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5718,12 +5718,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5736,12 +5736,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5754,7 +5754,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>7.57am</t>
+          <t>7.56am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5934,19 +5934,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>17 min · 11 km · live traffic · 10 min loading first</t>
+          <t>16 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>7.57am</t>
+          <t>7.56am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.07am</t>
+          <t>8.06am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5959,12 +5959,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.07am</t>
+          <t>8.06am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5977,12 +5977,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.32am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5995,7 +5995,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.32am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6108,19 +6108,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>44 min · 29 km · live traffic</t>
+          <t>43 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.04pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6133,12 +6133,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.04pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6151,7 +6151,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6434,19 +6434,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 14 km · live traffic · 10 min loading first</t>
+          <t>27 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6459,12 +6459,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6477,12 +6477,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6495,7 +6495,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6682,19 +6682,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 14 km · live traffic · 10 min loading first</t>
+          <t>27 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6707,12 +6707,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6725,12 +6725,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6743,7 +6743,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1398,19 +1398,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>25 min · 13 km · live traffic · 10 min loading first</t>
+          <t>26 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1423,7 +1423,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1592,19 +1592,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>26 min · 12 km · live traffic · 10 min loading first</t>
+          <t>29 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1617,12 +1617,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1765,7 +1765,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>11 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.20am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2240,19 +2240,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>40 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>35 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.20am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.30am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2265,12 +2265,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.30am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.40am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2283,12 +2283,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.40am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.55am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.55am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>3.06pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -2413,12 +2413,12 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>3.06pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>3.14pm</t>
+          <t>3.15pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -2428,19 +2428,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>17 min · 5 km · traffic, refreshed hourly</t>
+          <t>9 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>3.14pm</t>
+          <t>3.15pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>3.59pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -2453,12 +2453,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>3.59pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>4.29pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2471,12 +2471,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>4.29pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2581,7 +2581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2658,19 +2658,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>42 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>45 min · 24 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2683,12 +2683,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.45am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2701,12 +2701,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.45am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.57am</t>
+          <t>10.00am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2716,60 +2716,60 @@
       </c>
       <c r="D10" s="7" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>9.57am</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>10.00am</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>1.00pm</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY WORKSHOP</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>1.05pm</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>1.00pm</t>
+          <t>1.05pm</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>1.05pm</t>
+          <t>1.20pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
@@ -2777,17 +2777,17 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>1.05pm</t>
+          <t>1.20pm</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>1.20pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Hold at Mandala Cultural Centre</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr"/>
@@ -2800,70 +2800,70 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
+          <t>2.20pm</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Lunch near Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
           <t>4.30pm</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Hold at Mandala Cultural Centre</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>1.20pm</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>2.20pm</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Lunch near Mandala Cultural Centre</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr"/>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>→ Leave Mandala Cultural Centre for Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>0 min · 0 km</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>4.30pm</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>4.30pm</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>→ Leave Mandala Cultural Centre for Mandala Cultural Centre</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>0 min · 0 km</t>
-        </is>
-      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr"/>
@@ -2871,75 +2871,75 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>6.30pm</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>8.00pm</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>INDONESIAN × INDIAN PUPPETRY ACT</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>Performance · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
         </is>
       </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>8.50pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -2947,38 +2947,20 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>8.50pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>8.50pm</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>8.50pm</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>Dinner near Mandala Cultural Centre</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>
@@ -3083,7 +3065,7 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>18 min · 4 km · typical traffic for the day · 10 min loading first</t>
+          <t>18 min · 4 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3456,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>4.16pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -3505,7 +3487,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>4.16pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -3520,7 +3502,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>9 min · 2 km · typical traffic for the day</t>
+          <t>8 min · 2 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5412,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5440,19 +5422,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>33 min · 19 km · live traffic · 10 min loading first</t>
+          <t>35 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5465,12 +5447,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5483,7 +5465,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6098,7 +6080,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.29pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6108,19 +6090,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>43 min · 29 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.29pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>1.59pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6133,12 +6115,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>1.59pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.29pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6151,12 +6133,12 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.29pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>3.29pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -6424,7 +6406,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6434,19 +6416,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 14 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6459,12 +6441,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6477,12 +6459,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6495,7 +6477,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6672,7 +6654,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6682,19 +6664,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 14 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6707,12 +6689,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6725,12 +6707,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6743,7 +6725,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -784,7 +784,11 @@
           <t>9.50pm · Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>“Shadow Puppetry Performance”: arrives 1.43pm, 13 min late for the 120 min preparation.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1388,7 +1392,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1398,19 +1402,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>26 min · 14 km · live traffic · 10 min loading first</t>
+          <t>35 min · 16 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.50pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1423,7 +1427,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.50pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -1582,7 +1586,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1592,19 +1596,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>29 min · 15 km · live traffic · 10 min loading first</t>
+          <t>35 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1617,12 +1621,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1635,12 +1639,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1653,7 +1657,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -1734,7 +1738,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1765,7 +1769,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1780,7 +1784,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>11 min · 5 km · live traffic</t>
+          <t>12 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2234,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2240,19 +2244,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 20 km · live traffic · 10 min loading first</t>
+          <t>38 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2265,12 +2269,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.38am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2283,12 +2287,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.38am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.53am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2301,7 +2305,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.53am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2382,7 +2386,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>3.06pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -2413,7 +2417,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>3.06pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -2428,7 +2432,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>9 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2648,7 +2652,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2658,19 +2662,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>45 min · 24 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>38 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2683,12 +2687,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.45am</t>
+          <t>9.38am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2701,75 +2705,75 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.45am</t>
+          <t>9.38am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
+          <t>9.53am</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>9.53am</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>1.00pm</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY WORKSHOP</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>1.05pm</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
           <t>1.05pm</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>1.20pm</t>
-        </is>
-      </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
@@ -2777,17 +2781,17 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
+          <t>1.05pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>4.30pm</t>
-        </is>
-      </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Hold at Mandala Cultural Centre</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr"/>
@@ -2800,70 +2804,70 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Hold at Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>1.20pm</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
           <t>2.20pm</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Lunch near Mandala Cultural Centre</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>4.30pm</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>4.30pm</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>→ Leave Mandala Cultural Centre for Mandala Cultural Centre</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>0 min · 0 km</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>4.30pm</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr"/>
@@ -2871,75 +2875,75 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
           <t>5.30pm</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>8.00pm</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>INDONESIAN × INDIAN PUPPETRY ACT</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Performance · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>8.00pm</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>8.20pm</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
           <t>8.20pm</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>8.50pm</t>
-        </is>
-      </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -2947,20 +2951,38 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
           <t>8.50pm</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Dinner near Mandala Cultural Centre</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D24" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>
@@ -3304,7 +3326,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -3314,19 +3336,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>26 min · 8 km · typical traffic for the day · 10 min loading first</t>
+          <t>31 min · 9 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3339,12 +3361,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3357,12 +3379,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3375,7 +3397,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3502,7 +3524,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>8 min · 2 km · typical traffic for the day</t>
+          <t>8 min · 2 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4853,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.06pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4841,19 +4863,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>39 min · 34 km · live traffic · 10 min loading first</t>
+          <t>41 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.06pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.34pm</t>
+          <t>6.36pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5412,7 +5434,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.28am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5422,19 +5444,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>35 min · 20 km · live traffic · 10 min loading first</t>
+          <t>38 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.28am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.38am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5447,12 +5469,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.38am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.53am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5465,7 +5487,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.53am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5665,7 +5687,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.59pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5675,19 +5697,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>13 min · 7 km · live traffic · 10 min loading first</t>
+          <t>14 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.59pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.29pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5700,12 +5722,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.29pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.59pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5718,12 +5740,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.59pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.59pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5736,7 +5758,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.59pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5906,7 +5928,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>7.56am</t>
+          <t>7.58am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5916,19 +5938,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>16 min · 11 km · live traffic · 10 min loading first</t>
+          <t>18 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>7.56am</t>
+          <t>7.58am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.06am</t>
+          <t>8.08am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5941,12 +5963,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.06am</t>
+          <t>8.08am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5959,12 +5981,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5977,7 +5999,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6080,7 +6102,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.29pm</t>
+          <t>1.43pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6090,19 +6112,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic</t>
+          <t>53 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.29pm</t>
+          <t>1.43pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>1.59pm</t>
+          <t>2.13pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6115,12 +6137,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>1.59pm</t>
+          <t>2.13pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.29pm</t>
+          <t>2.43pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6133,12 +6155,12 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.29pm</t>
+          <t>2.43pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>3.29pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -6406,7 +6428,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6416,19 +6438,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>42 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6441,12 +6463,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6459,12 +6481,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.57pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6477,7 +6499,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.57pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6654,7 +6676,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6664,19 +6686,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>42 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6689,12 +6711,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6707,12 +6729,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.57pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6725,7 +6747,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.57pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -784,11 +784,7 @@
           <t>9.50pm · Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>“Shadow Puppetry Performance”: arrives 1.43pm, 13 min late for the 120 min preparation.</t>
-        </is>
-      </c>
+      <c r="G10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1264,27 +1260,23 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Closing Day 11.00am</t>
+          <t>The Finale 6.30pm</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>9.55am</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>Sabha Bengaluru</t>
-        </is>
-      </c>
+          <t>3.35pm</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr"/>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>10.10pm · Dinner near Sabha Bengaluru (late return)</t>
+          <t>8.50pm · Dinner before leaving</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2 of 25 artists travel today; 23 stay at the stay.</t>
+          <t>Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1384,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1402,19 +1394,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 16 km · live traffic · 10 min loading first</t>
+          <t>25 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
           <t>4.40pm</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>4.50pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1427,7 +1419,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.50pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -1586,7 +1578,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1596,19 +1588,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 15 km · live traffic · 10 min loading first</t>
+          <t>27 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1621,12 +1613,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1639,12 +1631,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1657,7 +1649,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -1738,7 +1730,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1769,7 +1761,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1784,7 +1776,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>12 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2244,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>38 min · 24 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2269,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.38am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2287,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.38am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.53am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2305,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.53am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2386,7 +2378,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>3.05pm</t>
+          <t>3.06pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -2417,7 +2409,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>3.05pm</t>
+          <t>3.06pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -2432,7 +2424,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>9 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2662,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>38 min · 24 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2687,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.38am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2705,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.38am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.53am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2723,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.53am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3077,7 +3069,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>3.33pm</t>
+          <t>3.23pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -3087,19 +3079,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>18 min · 4 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>8 min · 4 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.33pm</t>
+          <t>3.23pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.03pm</t>
+          <t>3.53pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3112,12 +3104,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.03pm</t>
+          <t>3.53pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.33pm</t>
+          <t>4.23pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3130,12 +3122,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.33pm</t>
+          <t>4.23pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.23pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3148,7 +3140,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.23pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -3326,7 +3318,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -3336,19 +3328,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>31 min · 9 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>16 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3361,12 +3353,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3379,12 +3371,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
+          <t>9.16am</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
           <t>9.31am</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>9.46am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3397,7 +3389,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3478,7 +3470,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.21pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -3509,7 +3501,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.21pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -3524,7 +3516,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>8 min · 2 km · traffic, refreshed hourly</t>
+          <t>4 min · 2 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3729,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3747,19 +3739,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>26 min · 8 km · typical traffic for the day · 10 min loading first</t>
+          <t>31 min · 9 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3772,12 +3764,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3790,12 +3782,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3808,7 +3800,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -3899,7 +3891,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>29 min · 8 km · typical traffic for the day</t>
+          <t>29 min · 8 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3957,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>35 min · 9 km · typical traffic for the day · 10 min loading first</t>
+          <t>42 min · 10 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>5.57pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3982,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>5.57pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.20pm</t>
+          <t>6.27pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -4000,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.20pm</t>
+          <t>6.27pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.27pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4018,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.27pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4141,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 32 · 413 km · typical traffic for the day · sleep on the road</t>
+          <t>7 h 32 · 413 km · traffic, refreshed hourly · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4222,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 32 · 413 km · typical traffic for the day · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 32 · 413 km · traffic, refreshed hourly · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>8 h 04 · 393 km · typical traffic for the day · home about 5.35am (+1)</t>
+          <t>8 h · 393 km · traffic, refreshed hourly · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4550,7 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>12.28pm</t>
+          <t>12.22pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4589,12 +4581,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>12.28pm</t>
+          <t>12.22pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>12.58pm</t>
+          <t>12.52pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -4607,7 +4599,7 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>12.58pm</t>
+          <t>12.52pm</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
@@ -4622,7 +4614,7 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>52 min · 15 km · typical traffic for the day · 10 min loading first</t>
+          <t>58 min · 16 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4845,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.06pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4863,19 +4855,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>41 min · 34 km · live traffic · 10 min loading first</t>
+          <t>38 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.06pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.36pm</t>
+          <t>6.33pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -4919,7 +4911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4945,171 +4937,199 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Closing Day 11.00am</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+          <t>The Finale 6.30pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>• Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Where / detail</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>9.55am</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>10.20am</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Sabha Bengaluru</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>15 min · 5 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>10.20am</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>10.30am</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr"/>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>3.35pm</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>→ Leave the stay for Suchitra Cinema and Cultural Academy - Amphitheatre</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>travel time unknown</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>10.30am</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>11.00am</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Spare time at the venue</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
     </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>11.00am</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>CLOSING DAY</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Talk · Sabha Bengaluru, Shivajinagar · 2 artists</t>
-        </is>
-      </c>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>During “Closing Day” — arrange packed lunch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>10.10pm</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr"/>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>THE FINALE</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>10.10pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>11.10pm</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near Sabha Bengaluru (late return)</t>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Dinner before leaving</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>added: the plan has dinner back at the stay</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5434,7 +5454,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.28am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5444,19 +5464,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>38 min · 24 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.28am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.38am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5469,12 +5489,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.38am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.53am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5487,7 +5507,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.53am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5687,7 +5707,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>2.59pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5697,19 +5717,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>14 min · 7 km · live traffic · 10 min loading first</t>
+          <t>12 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2.59pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.29pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5722,12 +5742,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.29pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3.59pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5740,12 +5760,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>3.59pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.59pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5758,7 +5778,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.59pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5928,7 +5948,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>7.58am</t>
+          <t>7.56am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5938,19 +5958,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>18 min · 11 km · live traffic · 10 min loading first</t>
+          <t>16 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>7.58am</t>
+          <t>7.56am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.08am</t>
+          <t>8.06am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5963,12 +5983,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.08am</t>
+          <t>8.06am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5981,12 +6001,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.33am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5999,7 +6019,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.33am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6102,7 +6122,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.43pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6112,19 +6132,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>53 min · 26 km · live traffic</t>
+          <t>41 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.43pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.13pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6137,12 +6157,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.13pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.43pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6155,7 +6175,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.43pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -6428,7 +6448,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6438,19 +6458,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>42 min · 18 km · live traffic · 10 min loading first</t>
+          <t>27 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6463,12 +6483,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6481,12 +6501,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
+          <t>5.27pm</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
           <t>5.42pm</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>5.57pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6499,7 +6519,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.57pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6676,7 +6696,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6686,19 +6706,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>42 min · 18 km · live traffic · 10 min loading first</t>
+          <t>27 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6711,12 +6731,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6729,12 +6749,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
+          <t>5.27pm</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
           <t>5.42pm</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>5.57pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6747,7 +6767,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.57pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.17am</t>
+          <t>7.05am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1394,19 +1394,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>25 min · 14 km · live traffic · 10 min loading first</t>
+          <t>26 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -3328,19 +3328,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>16 min · 9 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3389,7 +3389,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>31 min · 9 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3764,12 +3764,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.49pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>29 min · 8 km · traffic, refreshed hourly</t>
+          <t>14 min · 8 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.49pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.49pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>42 min · 10 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>18 min · 10 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.57pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.57pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.27pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.27pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.27pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.27pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 32 · 413 km · traffic, refreshed hourly · sleep on the road</t>
+          <t>7 h 20 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.17am</t>
+          <t>7.05am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 32 · 413 km · traffic, refreshed hourly · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 20 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.17am</t>
+          <t>7.05am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.47am</t>
+          <t>8.35am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.47am</t>
+          <t>8.35am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.05am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.05am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>8 h · 393 km · traffic, refreshed hourly · home about 5.35am (+1)</t>
+          <t>7 h 21 · 401 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>58 min · 16 km · typical traffic for the day · 10 min loading first</t>
+          <t>58 min · 16 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4855,19 +4855,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>38 min · 34 km · live traffic · 10 min loading first</t>
+          <t>39 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.33pm</t>
+          <t>6.34pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.35pm</t>
+          <t>9.33pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5247,14 +5247,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>55 min · 33 km · typical traffic for the day</t>
+          <t>53 min · 33 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.35pm</t>
+          <t>9.33pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6132,19 +6132,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>41 min · 29 km · live traffic</t>
+          <t>42 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6157,12 +6157,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6175,7 +6175,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6458,19 +6458,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6483,12 +6483,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6501,12 +6501,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6519,7 +6519,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6706,19 +6706,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6731,12 +6731,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6749,12 +6749,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6767,7 +6767,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.05am</t>
+          <t>7.12am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.32pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1394,19 +1394,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>26 min · 14 km · live traffic · 10 min loading first</t>
+          <t>27 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.32pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1588,19 +1588,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 15 km · live traffic · 10 min loading first</t>
+          <t>29 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1631,12 +1631,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1649,7 +1649,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>12 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>36 min · 23 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>36 min · 23 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>3.23pm</t>
+          <t>3.24pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>8 min · 4 km · live traffic · 10 min loading first</t>
+          <t>9 min · 4 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.23pm</t>
+          <t>3.24pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3.53pm</t>
+          <t>3.54pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3104,12 +3104,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>3.53pm</t>
+          <t>3.54pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.23pm</t>
+          <t>4.24pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.23pm</t>
+          <t>4.24pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>5.23pm</t>
+          <t>5.24pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3140,7 +3140,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>5.23pm</t>
+          <t>5.24pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>14 min · 8 km · live traffic</t>
+          <t>15 min · 8 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>18 min · 10 km · live traffic · 10 min loading first</t>
+          <t>19 min · 10 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.34pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.34pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.04pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.04pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 20 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 27 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.05am</t>
+          <t>7.12am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 20 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 27 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.05am</t>
+          <t>7.12am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.35am</t>
+          <t>8.42am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.35am</t>
+          <t>8.42am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.05am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.05am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 21 · 401 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 06 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>12.22pm</t>
+          <t>12.35pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4581,12 +4581,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>12.22pm</t>
+          <t>12.35pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>12.52pm</t>
+          <t>1.05pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -4599,12 +4599,12 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>12.52pm</t>
+          <t>1.05pm</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>2.00pm</t>
+          <t>1.42pm</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -4614,19 +4614,19 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>58 min · 16 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>27 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>2.00pm</t>
+          <t>1.42pm</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>2.30pm</t>
+          <t>2.12pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2.30pm</t>
+          <t>2.12pm</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>3.00pm</t>
+          <t>2.42pm</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -4657,75 +4657,75 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>3.00pm</t>
+          <t>2.42pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
+          <t>3.42pm</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>3.42pm</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
           <t>4.00pm</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>4.00pm</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>5.30pm</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>BALINESE DANCE DEMONSTRATION</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>Performance · Indian Music Experience Museum, JP Nagar 7th Phase · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>5.50pm</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
           <t>5.50pm</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>6.20pm</t>
-        </is>
-      </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr"/>
@@ -4733,20 +4733,38 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
+          <t>5.50pm</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
           <t>6.20pm</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>6.20pm</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>7.20pm</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>Dinner near Indian Music Experience Museum</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D20" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>
@@ -4845,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4855,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>39 min · 34 km · live traffic · 10 min loading first</t>
+          <t>43 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.34pm</t>
+          <t>6.38pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5247,7 +5265,7 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>53 min · 33 km · typical traffic for the day</t>
+          <t>53 min · 33 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.26am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5464,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>36 min · 23 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.26am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.36am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5489,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.36am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.51am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5507,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.51am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5707,7 +5725,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5717,19 +5735,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>12 min · 7 km · live traffic · 10 min loading first</t>
+          <t>13 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5742,12 +5760,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5760,12 +5778,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5778,7 +5796,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5948,7 +5966,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>7.56am</t>
+          <t>7.58am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5958,19 +5976,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>16 min · 11 km · live traffic · 10 min loading first</t>
+          <t>18 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>7.56am</t>
+          <t>7.58am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.06am</t>
+          <t>8.08am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5983,12 +6001,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.06am</t>
+          <t>8.08am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6001,12 +6019,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6019,7 +6037,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6122,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.32pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6132,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>42 min · 29 km · live traffic</t>
+          <t>43 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.32pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.02pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6157,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.02pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.32pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6175,7 +6193,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.32pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.12am</t>
+          <t>7.27am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1588,19 +1588,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>29 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1631,12 +1631,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1649,7 +1649,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>12 min · 5 km · live traffic</t>
+          <t>11 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>36 min · 23 km · live traffic · 10 min loading first</t>
+          <t>35 min · 23 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>36 min · 23 km · live traffic · 10 min loading first</t>
+          <t>35 min · 23 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>3.24pm</t>
+          <t>3.23pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>9 min · 4 km · live traffic · 10 min loading first</t>
+          <t>8 min · 4 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.24pm</t>
+          <t>3.23pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3.54pm</t>
+          <t>3.53pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3104,12 +3104,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>3.54pm</t>
+          <t>3.53pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.24pm</t>
+          <t>4.23pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.24pm</t>
+          <t>4.23pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>5.24pm</t>
+          <t>5.23pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3140,7 +3140,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>5.24pm</t>
+          <t>5.23pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>15 min · 8 km · live traffic</t>
+          <t>14 min · 8 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.35pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>19 min · 10 km · live traffic · 10 min loading first</t>
+          <t>18 min · 10 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.34pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.34pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.04pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.04pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 27 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 42 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.12am</t>
+          <t>7.27am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 27 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 42 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.12am</t>
+          <t>7.27am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.42am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.42am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.57am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.57am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 06 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 10 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4873,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>43 min · 34 km · live traffic · 10 min loading first</t>
+          <t>39 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.38pm</t>
+          <t>6.34pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.26am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>36 min · 23 km · live traffic · 10 min loading first</t>
+          <t>35 min · 23 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.26am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.36am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.36am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.51am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.51am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5735,19 +5735,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>13 min · 7 km · live traffic · 10 min loading first</t>
+          <t>12 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5760,12 +5760,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5778,12 +5778,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5796,7 +5796,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5906,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>7.58am</t>
+          <t>7.56am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5976,19 +5976,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>18 min · 11 km · live traffic · 10 min loading first</t>
+          <t>16 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>7.58am</t>
+          <t>7.56am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.08am</t>
+          <t>8.06am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -6001,12 +6001,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.08am</t>
+          <t>8.06am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6019,12 +6019,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.33am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6037,7 +6037,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.33am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>43 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,97 +6193,97 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6291,20 +6291,38 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.27am</t>
+          <t>6.53am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1394,19 +1394,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 14 km · live traffic · 10 min loading first</t>
+          <t>26 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>11 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 23 km · live traffic · 10 min loading first</t>
+          <t>34 min · 23 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 23 km · live traffic · 10 min loading first</t>
+          <t>34 min · 23 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -3328,19 +3328,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>17 min · 9 km · live traffic · 10 min loading first</t>
+          <t>16 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3389,7 +3389,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>17 min · 9 km · live traffic · 10 min loading first</t>
+          <t>16 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3764,12 +3764,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>14 min · 8 km · live traffic</t>
+          <t>15 min · 7 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 42 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 08 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.27am</t>
+          <t>6.53am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 42 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 08 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.27am</t>
+          <t>6.53am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.23am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.57am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.57am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 10 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>6 h 52 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>1.42pm</t>
+          <t>1.41pm</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -4614,19 +4614,19 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>27 min · 14 km · live traffic · 10 min loading first</t>
+          <t>26 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>1.42pm</t>
+          <t>1.41pm</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>2.12pm</t>
+          <t>2.11pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2.12pm</t>
+          <t>2.11pm</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>2.42pm</t>
+          <t>2.41pm</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -4657,12 +4657,12 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>2.42pm</t>
+          <t>2.41pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -4675,7 +4675,7 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4873,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>39 min · 34 km · live traffic · 10 min loading first</t>
+          <t>38 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.34pm</t>
+          <t>6.33pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.33pm</t>
+          <t>9.15pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,14 +5265,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>53 min · 33 km · traffic, refreshed hourly</t>
+          <t>35 min · 33 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.33pm</t>
+          <t>9.15pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>35 min · 23 km · live traffic · 10 min loading first</t>
+          <t>34 min · 23 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5906,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>41 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,12 +6193,12 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -6208,38 +6208,42 @@
       </c>
       <c r="D18" s="7" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>3.28pm</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr"/>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -6248,42 +6252,38 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6291,38 +6291,20 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>6.53am</t>
+          <t>7.21am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1588,19 +1588,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>27 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1631,12 +1631,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1649,7 +1649,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>15 min · 7 km · live traffic</t>
+          <t>14 min · 7 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.35pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 08 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 36 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>6.53am</t>
+          <t>7.21am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 08 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 36 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>6.53am</t>
+          <t>7.21am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.23am</t>
+          <t>8.51am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.23am</t>
+          <t>8.51am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>6 h 52 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 11 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.25pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>41 min · 29 km · live traffic</t>
+          <t>35 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.25pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.25pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,97 +6193,97 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.25pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
+          <t>3.25pm</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>3.25pm</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6291,20 +6291,38 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6466,7 +6484,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6476,19 +6494,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>27 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6501,12 +6519,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6519,12 +6537,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6537,7 +6555,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6714,7 +6732,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6724,19 +6742,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>27 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6749,12 +6767,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6767,12 +6785,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6785,7 +6803,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.21am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1394,19 +1394,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>26 min · 14 km · live traffic · 10 min loading first</t>
+          <t>25 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>11 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>34 min · 23 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>34 min · 23 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>14 min · 7 km · live traffic</t>
+          <t>14 min · 8 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>18 min · 10 km · live traffic · 10 min loading first</t>
+          <t>17 min · 10 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.02pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.02pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.02pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.02pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 36 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 26 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.21am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 36 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 26 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.21am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.51am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.51am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 11 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 25 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>1.41pm</t>
+          <t>1.40pm</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -4614,19 +4614,19 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>26 min · 14 km · live traffic · 10 min loading first</t>
+          <t>25 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>1.41pm</t>
+          <t>1.40pm</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>2.11pm</t>
+          <t>2.10pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2.11pm</t>
+          <t>2.10pm</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>2.41pm</t>
+          <t>2.40pm</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -4657,12 +4657,12 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>2.41pm</t>
+          <t>2.40pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.40pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -4675,7 +4675,7 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.40pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>34 min · 23 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.25pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>35 min · 26 km · live traffic</t>
+          <t>41 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.25pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.25pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,12 +6193,12 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.25pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>3.25pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -6208,38 +6208,42 @@
       </c>
       <c r="D18" s="7" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>3.25pm</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr"/>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -6248,42 +6252,38 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6291,38 +6291,20 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>11 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>33 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>33 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>17 min · 10 km · live traffic · 10 min loading first</t>
+          <t>18 min · 10 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.02pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.02pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.02pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.02pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 26 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 21 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 26 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 21 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 25 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 21 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4873,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>38 min · 34 km · live traffic · 10 min loading first</t>
+          <t>37 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.33pm</t>
+          <t>6.32pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.15pm</t>
+          <t>9.14pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,14 +5265,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>35 min · 33 km · live traffic</t>
+          <t>34 min · 33 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.15pm</t>
+          <t>9.14pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>33 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>7.56am</t>
+          <t>7.55am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5976,19 +5976,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>16 min · 11 km · live traffic · 10 min loading first</t>
+          <t>15 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>7.56am</t>
+          <t>7.55am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.06am</t>
+          <t>8.05am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -6001,12 +6001,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.06am</t>
+          <t>8.05am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.15am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6019,12 +6019,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.15am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6037,7 +6037,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>41 min · 26 km · live traffic</t>
+          <t>40 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.00pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.00pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.30pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,7 +6193,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.30pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.00am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.32pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1394,19 +1394,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>25 min · 14 km · live traffic · 10 min loading first</t>
+          <t>27 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.32pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1588,19 +1588,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1631,12 +1631,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1649,7 +1649,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>33 min · 20 km · live traffic · 10 min loading first</t>
+          <t>35 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>33 min · 20 km · live traffic · 10 min loading first</t>
+          <t>35 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>3.23pm</t>
+          <t>3.24pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>8 min · 4 km · live traffic · 10 min loading first</t>
+          <t>9 min · 4 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.23pm</t>
+          <t>3.24pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3.53pm</t>
+          <t>3.54pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3104,12 +3104,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>3.53pm</t>
+          <t>3.54pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.23pm</t>
+          <t>4.24pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.23pm</t>
+          <t>4.24pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>5.23pm</t>
+          <t>5.24pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3140,7 +3140,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>5.23pm</t>
+          <t>5.24pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.58am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -3328,19 +3328,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>16 min · 9 km · live traffic · 10 min loading first</t>
+          <t>18 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.58am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3389,7 +3389,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.58am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>16 min · 9 km · live traffic · 10 min loading first</t>
+          <t>18 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.58am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3764,12 +3764,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>14 min · 8 km · live traffic</t>
+          <t>15 min · 8 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>18 min · 10 km · live traffic · 10 min loading first</t>
+          <t>19 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.34pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.34pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.04pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.04pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 21 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 15 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.00am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 21 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 15 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.00am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.00am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.00am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.30am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.30am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 21 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 20 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>1.40pm</t>
+          <t>1.42pm</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -4614,19 +4614,19 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>25 min · 14 km · live traffic · 10 min loading first</t>
+          <t>27 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>1.40pm</t>
+          <t>1.42pm</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>2.10pm</t>
+          <t>2.12pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2.10pm</t>
+          <t>2.12pm</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>2.40pm</t>
+          <t>2.42pm</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -4657,12 +4657,12 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>2.40pm</t>
+          <t>2.42pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>3.40pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -4675,7 +4675,7 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>3.40pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4873,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>37 min · 34 km · live traffic · 10 min loading first</t>
+          <t>39 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.32pm</t>
+          <t>6.34pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.14pm</t>
+          <t>9.16pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,14 +5265,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>34 min · 33 km · live traffic</t>
+          <t>36 min · 33 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.14pm</t>
+          <t>9.16pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>33 min · 20 km · live traffic · 10 min loading first</t>
+          <t>35 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5735,19 +5735,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>12 min · 7 km · live traffic · 10 min loading first</t>
+          <t>13 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5760,12 +5760,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5778,12 +5778,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5796,7 +5796,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5906,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>7.55am</t>
+          <t>7.57am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5976,19 +5976,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>15 min · 11 km · live traffic · 10 min loading first</t>
+          <t>17 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>7.55am</t>
+          <t>7.57am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.05am</t>
+          <t>8.07am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -6001,12 +6001,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.05am</t>
+          <t>8.07am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.15am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6019,12 +6019,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.15am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6037,7 +6037,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.30pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.30pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.00pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.00pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.30pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,97 +6193,97 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.30pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6291,20 +6291,38 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6466,7 +6484,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6476,19 +6494,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 15 km · live traffic · 10 min loading first</t>
+          <t>29 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6501,12 +6519,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6519,12 +6537,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6537,7 +6555,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6714,7 +6732,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6724,19 +6742,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 15 km · live traffic · 10 min loading first</t>
+          <t>29 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6749,12 +6767,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6767,12 +6785,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6785,7 +6803,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1394,19 +1394,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 14 km · live traffic · 10 min loading first</t>
+          <t>26 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 20 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 20 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>3.24pm</t>
+          <t>3.23pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>9 min · 4 km · live traffic · 10 min loading first</t>
+          <t>8 min · 4 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.24pm</t>
+          <t>3.23pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3.54pm</t>
+          <t>3.53pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3104,12 +3104,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>3.54pm</t>
+          <t>3.53pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.24pm</t>
+          <t>4.23pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.24pm</t>
+          <t>4.23pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>5.24pm</t>
+          <t>5.23pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3140,7 +3140,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>5.24pm</t>
+          <t>5.23pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>8.58am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -3328,19 +3328,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>18 min · 9 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.58am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3389,7 +3389,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.58am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>18 min · 9 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.58am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3764,12 +3764,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>19 min · 9 km · live traffic · 10 min loading first</t>
+          <t>18 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.34pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.34pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.04pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.04pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 15 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 21 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 15 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 21 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.00am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.00am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.30am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.30am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 20 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 01 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>1.42pm</t>
+          <t>1.41pm</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -4614,19 +4614,19 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>27 min · 14 km · live traffic · 10 min loading first</t>
+          <t>26 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>1.42pm</t>
+          <t>1.41pm</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>2.12pm</t>
+          <t>2.11pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2.12pm</t>
+          <t>2.11pm</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>2.42pm</t>
+          <t>2.41pm</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -4657,12 +4657,12 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>2.42pm</t>
+          <t>2.41pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -4675,7 +4675,7 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>35 min · 20 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5735,19 +5735,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>13 min · 7 km · live traffic · 10 min loading first</t>
+          <t>12 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5760,12 +5760,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5778,12 +5778,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5796,7 +5796,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5906,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>42 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,12 +6193,12 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -6208,38 +6208,42 @@
       </c>
       <c r="D18" s="7" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>3.28pm</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr"/>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -6248,42 +6252,38 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6291,38 +6291,20 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6484,7 +6466,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6494,19 +6476,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>29 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6519,12 +6501,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6537,12 +6519,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6555,7 +6537,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6732,7 +6714,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6742,19 +6724,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>29 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6767,12 +6749,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6785,12 +6767,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6803,7 +6785,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.23am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1394,19 +1394,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>26 min · 14 km · live traffic · 10 min loading first</t>
+          <t>25 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.31pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>33 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>33 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -3328,19 +3328,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>17 min · 9 km · live traffic · 10 min loading first</t>
+          <t>16 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3389,7 +3389,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>17 min · 9 km · live traffic · 10 min loading first</t>
+          <t>16 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3764,12 +3764,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>15 min · 8 km · live traffic</t>
+          <t>14 min · 8 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.35pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>18 min · 9 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.02pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.02pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.02pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.02pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 21 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 38 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.23am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 21 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 38 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.23am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.53am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.53am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 01 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 05 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>1.41pm</t>
+          <t>1.40pm</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -4614,19 +4614,19 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>26 min · 14 km · live traffic · 10 min loading first</t>
+          <t>25 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>1.41pm</t>
+          <t>1.40pm</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>2.11pm</t>
+          <t>2.10pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2.11pm</t>
+          <t>2.10pm</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>2.41pm</t>
+          <t>2.40pm</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -4657,12 +4657,12 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>2.41pm</t>
+          <t>2.40pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.40pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -4675,7 +4675,7 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.40pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4873,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>39 min · 34 km · live traffic · 10 min loading first</t>
+          <t>37 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.34pm</t>
+          <t>6.32pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.16pm</t>
+          <t>9.13pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,14 +5265,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>36 min · 33 km · live traffic</t>
+          <t>33 min · 33 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.16pm</t>
+          <t>9.13pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>33 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5906,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>7.57am</t>
+          <t>7.56am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5976,19 +5976,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>17 min · 11 km · live traffic · 10 min loading first</t>
+          <t>16 min · 11 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>7.57am</t>
+          <t>7.56am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.07am</t>
+          <t>8.06am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -6001,12 +6001,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.07am</t>
+          <t>8.06am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6019,12 +6019,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.32am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6037,7 +6037,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.32am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.32pm</t>
+          <t>1.24pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>42 min · 26 km · live traffic</t>
+          <t>34 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.32pm</t>
+          <t>1.24pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.02pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.02pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.32pm</t>
+          <t>2.24pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,97 +6193,97 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.32pm</t>
+          <t>2.24pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
+          <t>3.24pm</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>3.24pm</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6291,20 +6291,38 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6466,7 +6484,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.06pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6476,19 +6494,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>26 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.06pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.16pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6501,12 +6519,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.16pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.26pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6519,12 +6537,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.26pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6537,7 +6555,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6714,7 +6732,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.06pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6724,19 +6742,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>26 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.06pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.16pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6749,12 +6767,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.16pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.26pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6767,12 +6785,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.26pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6785,7 +6803,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.23am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>33 min · 20 km · live traffic · 10 min loading first</t>
+          <t>35 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>33 min · 20 km · live traffic · 10 min loading first</t>
+          <t>35 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>14 min · 8 km · live traffic</t>
+          <t>15 min · 7 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>17 min · 9 km · live traffic · 10 min loading first</t>
+          <t>18 min · 10 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.02pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.02pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.02pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.02pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 38 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 26 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.23am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 38 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 26 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.23am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.53am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.53am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 05 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 07 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4873,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>37 min · 34 km · live traffic · 10 min loading first</t>
+          <t>39 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.32pm</t>
+          <t>6.34pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.13pm</t>
+          <t>9.15pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,14 +5265,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>33 min · 33 km · live traffic</t>
+          <t>35 min · 33 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.13pm</t>
+          <t>9.15pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>33 min · 20 km · live traffic · 10 min loading first</t>
+          <t>35 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5906,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>16 min · 11 km · live traffic · 10 min loading first</t>
+          <t>16 min · 12 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.24pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>34 min · 26 km · live traffic</t>
+          <t>43 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.24pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.24pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,12 +6193,12 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.24pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>3.24pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -6208,38 +6208,42 @@
       </c>
       <c r="D18" s="7" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>3.24pm</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr"/>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -6248,42 +6252,38 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6291,38 +6291,20 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6484,7 +6466,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.06pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6494,19 +6476,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>26 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.06pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.16pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6519,12 +6501,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.16pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.26pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6537,12 +6519,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.26pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6555,7 +6537,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6732,7 +6714,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.06pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6742,19 +6724,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>26 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.06pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.16pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6767,12 +6749,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.16pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.26pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6785,12 +6767,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.26pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6803,7 +6785,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.14am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1588,19 +1588,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>27 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.18am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1631,12 +1631,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1649,7 +1649,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 20 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 20 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>15 min · 7 km · live traffic</t>
+          <t>14 min · 7 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.35pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.35pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>18 min · 10 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.02pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.03pm</t>
+          <t>6.02pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.02pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.02pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 26 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 29 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.14am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 26 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 29 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 07 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 12 · 401 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4873,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>39 min · 34 km · live traffic · 10 min loading first</t>
+          <t>38 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.34pm</t>
+          <t>6.33pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>35 min · 20 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>43 min · 26 km · live traffic</t>
+          <t>41 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,7 +6193,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6476,19 +6476,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>27 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6501,12 +6501,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6519,12 +6519,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6537,7 +6537,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6724,19 +6724,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>27 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.08pm</t>
+          <t>5.07pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6749,12 +6749,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6767,12 +6767,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6785,7 +6785,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.43pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.14am</t>
+          <t>7.07am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.32pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1394,19 +1394,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>25 min · 14 km · live traffic · 10 min loading first</t>
+          <t>27 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.32pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1588,19 +1588,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.08am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.18am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1631,12 +1631,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1649,7 +1649,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>36 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>36 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -3328,19 +3328,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>16 min · 9 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3389,7 +3389,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>16 min · 9 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3764,12 +3764,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>14 min · 7 km · live traffic</t>
+          <t>15 min · 7 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.35pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>17 min · 9 km · live traffic · 10 min loading first</t>
+          <t>19 min · 10 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.34pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.34pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.02pm</t>
+          <t>6.04pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.02pm</t>
+          <t>6.04pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.02pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.02pm</t>
+          <t>7.04pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 29 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 22 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.14am</t>
+          <t>7.07am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 29 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 22 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.14am</t>
+          <t>7.07am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 12 · 401 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 16 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>1.40pm</t>
+          <t>1.42pm</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -4614,19 +4614,19 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>25 min · 14 km · live traffic · 10 min loading first</t>
+          <t>27 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>1.40pm</t>
+          <t>1.42pm</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>2.10pm</t>
+          <t>2.12pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2.10pm</t>
+          <t>2.12pm</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>2.40pm</t>
+          <t>2.42pm</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -4657,12 +4657,12 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>2.40pm</t>
+          <t>2.42pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>3.40pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -4675,7 +4675,7 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>3.40pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.26am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>34 min · 20 km · live traffic · 10 min loading first</t>
+          <t>36 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.26am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.36am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.36am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.51am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.51am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>7.56am</t>
+          <t>7.57am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5976,19 +5976,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>16 min · 12 km · live traffic · 10 min loading first</t>
+          <t>17 min · 12 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>7.56am</t>
+          <t>7.57am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.06am</t>
+          <t>8.07am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -6001,12 +6001,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.06am</t>
+          <t>8.07am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6019,12 +6019,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6037,7 +6037,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6476,19 +6476,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 15 km · live traffic · 10 min loading first</t>
+          <t>29 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6501,12 +6501,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6519,12 +6519,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6537,7 +6537,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6724,19 +6724,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 15 km · live traffic · 10 min loading first</t>
+          <t>29 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.07pm</t>
+          <t>5.09pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6749,12 +6749,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6767,12 +6767,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6785,7 +6785,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.44pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.07am</t>
+          <t>6.58am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1394,19 +1394,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 14 km · live traffic · 10 min loading first</t>
+          <t>26 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.32pm</t>
+          <t>4.31pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 17 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>36 min · 20 km · live traffic · 10 min loading first</t>
+          <t>35 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>36 min · 20 km · live traffic · 10 min loading first</t>
+          <t>35 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -3328,19 +3328,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>17 min · 9 km · live traffic · 10 min loading first</t>
+          <t>16 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3389,7 +3389,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>17 min · 9 km · live traffic · 10 min loading first</t>
+          <t>16 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3764,12 +3764,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>19 min · 10 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.02pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.34pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.34pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.04pm</t>
+          <t>6.02pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.04pm</t>
+          <t>6.02pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.02pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.04pm</t>
+          <t>7.02pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 22 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 13 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.07am</t>
+          <t>6.58am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 22 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 13 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.07am</t>
+          <t>6.58am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>8.58am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>8.58am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 16 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 17 · 402 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>1.42pm</t>
+          <t>1.41pm</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -4614,19 +4614,19 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>27 min · 14 km · live traffic · 10 min loading first</t>
+          <t>26 min · 14 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>1.42pm</t>
+          <t>1.41pm</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>2.12pm</t>
+          <t>2.11pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2.12pm</t>
+          <t>2.11pm</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>2.42pm</t>
+          <t>2.41pm</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -4657,12 +4657,12 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>2.42pm</t>
+          <t>2.41pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -4675,7 +4675,7 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4873,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>38 min · 34 km · live traffic · 10 min loading first</t>
+          <t>39 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.03pm</t>
+          <t>5.04pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.33pm</t>
+          <t>6.34pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.15pm</t>
+          <t>9.16pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,14 +5265,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>35 min · 33 km · live traffic</t>
+          <t>36 min · 34 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.15pm</t>
+          <t>9.16pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.26am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>36 min · 20 km · live traffic · 10 min loading first</t>
+          <t>35 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.26am</t>
+          <t>6.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.36am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.36am</t>
+          <t>6.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.51am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.51am</t>
+          <t>6.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5735,19 +5735,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>12 min · 7 km · live traffic · 10 min loading first</t>
+          <t>13 min · 8 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5760,12 +5760,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.27pm</t>
+          <t>3.28pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5778,12 +5778,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.58pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5796,7 +5796,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>41 min · 29 km · live traffic</t>
+          <t>42 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,7 +6193,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6476,19 +6476,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>29 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6501,12 +6501,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6519,12 +6519,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6537,7 +6537,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6724,19 +6724,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>29 min · 15 km · live traffic · 10 min loading first</t>
+          <t>28 min · 15 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.09pm</t>
+          <t>5.08pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6749,12 +6749,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6767,12 +6767,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6785,7 +6785,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.44pm</t>
+          <t>5.43pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
+++ b/plan/tour-plan-citadel-sarovar-portico-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>6.58am</t>
+          <t>6.59am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 25 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 25 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -3328,19 +3328,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>16 min · 9 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3389,7 +3389,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>16 min · 9 km · live traffic · 10 min loading first</t>
+          <t>17 min · 9 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3764,12 +3764,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>15 min · 7 km · live traffic</t>
+          <t>15 min · 8 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>17 min · 9 km · live traffic · 10 min loading first</t>
+          <t>18 min · 10 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.02pm</t>
+          <t>5.03pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.02pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.02pm</t>
+          <t>6.03pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.02pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.02pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 13 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 14 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>6.58am</t>
+          <t>6.59am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 13 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 14 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>6.58am</t>
+          <t>6.59am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.58am</t>
+          <t>8.59am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.58am</t>
+          <t>8.59am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 17 · 402 km · live traffic · home about 5.35am (+1)</t>
+          <t>7 h 09 · 401 km · live traffic · home about 5.35am (+1)</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4873,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>39 min · 34 km · live traffic · 10 min loading first</t>
+          <t>40 min · 34 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.04pm</t>
+          <t>5.05pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.34pm</t>
+          <t>6.35pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.16pm</t>
+          <t>9.17pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,14 +5265,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>36 min · 34 km · live traffic</t>
+          <t>37 min · 33 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.16pm</t>
+          <t>9.17pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>35 min · 25 km · live traffic · 10 min loading first</t>
+          <t>34 min · 20 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.25am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.35am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.50am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5735,19 +5735,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>13 min · 8 km · live traffic · 10 min loading first</t>
+          <t>12 min · 7 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5760,12 +5760,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.27pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5778,12 +5778,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5796,7 +5796,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
